--- a/benchmark_prototype_(1).xlsx
+++ b/benchmark_prototype_(1).xlsx
@@ -425,36 +425,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>meta_data</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>topic</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>difficulty</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>question</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>problem_description</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>entry_point</t>
         </is>
@@ -464,27 +469,30 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>{'index': 1, 'question name': 'Jump Game II', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def jump(self, nums: List[int]) -&gt; int:\n ', 'topic': ['Array', 'Greedy', 'Dynamic Programming']}</t>
-        </is>
+      <c r="B2" t="n">
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>{'index': 1, 'question name': 'Jump Game II', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def jump(self, nums: List[int]) -&gt; int:\n ', 'topic': ['Array', 'Greedy', 'Dynamic Programming'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>['Array', 'Greedy', 'Dynamic Programming']</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Jump Game II</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>You are given a 0-indexed array of integers nums of length n. You are initially positioned at nums[0].
 Each element nums[i] represents the maximum length of a forward jump from index i. In other words, if you are at nums[i], you can jump to any nums[i + j] where:
@@ -500,7 +508,7 @@
 Output: 2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution:
     def jump(self, nums: List[int]) -&gt; int:
@@ -512,27 +520,30 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>{'index': 2, 'question name': 'Candy', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def candy(self, ratings: List[int]) -&gt; int:\n        ', 'topic': ['Array', 'Greedy']}</t>
-        </is>
+      <c r="B3" t="n">
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>{'index': 2, 'question name': 'Candy', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def candy(self, ratings: List[int]) -&gt; int:\n        ', 'topic': ['Array', 'Greedy'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>['Array', 'Greedy']</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Candy</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>There are n children standing in a line. Each child is assigned a rating value given in the integer array ratings.
 You are giving candies to these children subjected to the following requirements:
@@ -550,7 +561,7 @@
 The third child gets 1 candy because it satisfies the above two conditions.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution:
     def candy(self, ratings: List[int]) -&gt; int:
@@ -562,27 +573,30 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>{'index': 3, 'question name': 'Gas Station', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def canCompleteCircuit(self, gas: List[int], cost: List[int]) -&gt; int:\n                ', 'topic': ['Array', 'Greedy']}</t>
-        </is>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>{'index': 3, 'question name': 'Gas Station', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def canCompleteCircuit(self, gas: List[int], cost: List[int]) -&gt; int:\n                ', 'topic': ['Array', 'Greedy'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>['Array', 'Greedy']</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Gas Station</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>There are n gas stations along a circular route, where the amount of gas at the ith station is gas[i].
 You have a car with an unlimited gas tank and it costs cost[i] of gas to travel from the ith station to its next (i + 1)th station. You begin the journey with an empty tank at one of the gas stations.
@@ -610,7 +624,7 @@
 Therefore, you can't travel around the circuit once no matter where you start.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution:
     def canCompleteCircuit(self, gas: List[int], cost: List[int]) -&gt; int:
@@ -622,27 +636,30 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{'index': 4, 'question name': 'Queue Reconstruction by Height', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def reconstructQueue(self, people: List[List[int]]) -&gt; List[List[int]]:\n        ', 'topic': ['Array', 'Binary Trees', 'Sorting']}</t>
-        </is>
+      <c r="B5" t="n">
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>{'index': 4, 'question name': 'Queue Reconstruction by Height', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def reconstructQueue(self, people: List[List[int]]) -&gt; List[List[int]]:\n        ', 'topic': ['Array', 'Binary Trees', 'Sorting'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>['Array', 'Binary Trees', 'Sorting']</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Queue Reconstruction by Height</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>You are given an array of people, people, which are the attributes of some people in a queue (not necessarily in order). Each people[i] = [hi, ki] represents the ith person of height hi with exactly ki other people in front who have a height greater than or equal to hi.
 Reconstruct and return the queue that is represented by the input array people. The returned queue should be formatted as an array queue, where queue[j] = [hj, kj] is the attributes of the jth person in the queue (queue[0] is the person at the front of the queue).
@@ -667,7 +684,7 @@
 It is guaranteed that the queue can be reconstructed.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution:
     def reconstructQueue(self, people: List[List[int]]) -&gt; List[List[int]]:
@@ -679,27 +696,30 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{'index': 5, 'question name': 'Longest Increasing Subsequence', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def lengthOfLIS(self, nums: List[int]) -&gt; int:', 'topic': ['Array', 'Dynamic Programming']}</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>{'index': 5, 'question name': 'Longest Increasing Subsequence', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def lengthOfLIS(self, nums: List[int]) -&gt; int:', 'topic': ['Array', 'Dynamic Programming'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>['Array', 'Dynamic Programming']</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Longest Increasing Subsequence</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Given an integer array nums, return the length of the longest strictly increasing 
 subsequence
@@ -719,7 +739,7 @@
 -104 &lt;= nums[i] &lt;= 10^4</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>class Solution:
     def lengthOfLIS(self, nums: List[int]) -&gt; int:</t>
@@ -730,27 +750,30 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>{'index': 6, 'question name': 'Word Break', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def wordBreak(self, s: str, wordDict: List[str]) -&gt; bool:', 'topic': ['Array', 'Dynamic Programming']}</t>
-        </is>
+      <c r="B7" t="n">
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>{'index': 6, 'question name': 'Word Break', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def wordBreak(self, s: str, wordDict: List[str]) -&gt; bool:', 'topic': ['Array', 'Dynamic Programming'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>['Array', 'Dynamic Programming']</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Word Break</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Given a string s and a dictionary of strings wordDict, return true if s can be segmented into a space-separated sequence of one or more dictionary words.
 Note that the same word in the dictionary may be reused multiple times in the segmentation.
@@ -774,7 +797,7 @@
 All the strings of wordDict are unique.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>class Solution:
     def wordBreak(self, s: str, wordDict: List[str]) -&gt; bool:</t>
@@ -785,27 +808,30 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'index': 7, 'question name': 'Coin Change', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def coinChange(self, coins: List[int], amount: int) -&gt; int:', 'topic': ['Array', 'Dynamic Programming', 'BFS']}</t>
-        </is>
+      <c r="B8" t="n">
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>{'index': 7, 'question name': 'Coin Change', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def coinChange(self, coins: List[int], amount: int) -&gt; int:', 'topic': ['Array', 'Dynamic Programming', 'BFS'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>['Array', 'Dynamic Programming', 'BFS']</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Coin Change</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>You are given an integer array coins representing coins of different denominations and an integer amount representing a total amount of money.
 Return the fewest number of coins that you need to make up that amount. If that amount of money cannot be made up by any combination of the coins, return -1.
@@ -826,7 +852,7 @@
 0 &lt;= amount &lt;= 10^4</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>class Solution:
     def coinChange(self, coins: List[int], amount: int) -&gt; int:</t>
@@ -837,27 +863,30 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'index': 8, 'question name': 'Edit Distance', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def minDistance(self, word1: str, word2: str) -&gt; int:', 'topic': ['Dynamic Programming']}</t>
-        </is>
+      <c r="B9" t="n">
+        <v>7</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>{'index': 8, 'question name': 'Edit Distance', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def minDistance(self, word1: str, word2: str) -&gt; int:', 'topic': ['Dynamic Programming'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>['Dynamic Programming']</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Edit Distance</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Given two strings word1 and word2, return the minimum number of operations required to convert word1 to word2.
 You have the following three operations permitted on a word:
@@ -885,7 +914,7 @@
 word1 and word2 consist of lowercase English letters.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>class Solution:
     def minDistance(self, word1: str, word2: str) -&gt; int:</t>
@@ -896,27 +925,30 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'index': 9, 'question name': 'Word Search', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def exist(self, board: List[List[str]], word: str) -&gt; bool:', 'topic': ['Array', 'Backtracking', 'DFS']}</t>
-        </is>
+      <c r="B10" t="n">
+        <v>8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>{'index': 9, 'question name': 'Word Search', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def exist(self, board: List[List[str]], word: str) -&gt; bool:', 'topic': ['Array', 'Backtracking', 'DFS'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>['Array', 'Backtracking', 'DFS']</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Word Search</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Given an m x n grid of characters board and a string word, return true if word exists in the grid.
 The word can be constructed from letters of sequentially adjacent cells, where adjacent cells are horizontally or vertically neighboring. The same letter cell may not be used more than once.
@@ -937,7 +969,7 @@
 board and word consists of only lowercase and uppercase English letters.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>class Solution:
     def exist(self, board: List[List[str]], word: str) -&gt; bool:</t>
@@ -948,27 +980,30 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'index': 11, 'question name': 'Combination Sum', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def combinationSum(self, candidates: List[int], target: int) -&gt; List[List[int]]:', 'topic': ['Array', 'Backtracking']}</t>
-        </is>
+      <c r="B11" t="n">
+        <v>9</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>{'index': 11, 'question name': 'Combination Sum', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def combinationSum(self, candidates: List[int], target: int) -&gt; List[List[int]]:', 'topic': ['Array', 'Backtracking'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>['Array', 'Backtracking']</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Combination Sum</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Given an array of distinct integers candidates and a target integer target, return a list of all unique combinations of candidates where the chosen numbers sum to target. You may return the combinations in any order.
 The same number may be chosen from candidates an unlimited number of times. Two combinations are unique if the 
@@ -995,7 +1030,7 @@
 1 &lt;= target &lt;= 40</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>class Solution:
     def combinationSum(self, candidates: List[int], target: int) -&gt; List[List[int]]:</t>
@@ -1006,27 +1041,30 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'index': 13, 'question name': 'Merge k Sorted Lists', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def mergeKLists(self, lists: List[Optional[ListNode]]) -&gt; Optional[ListNode]:', 'topic': ['Linked Lists', 'Divide and Conquer', 'Sorting']}</t>
-        </is>
+      <c r="B12" t="n">
+        <v>10</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>{'index': 13, 'question name': 'Merge k Sorted Lists', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def mergeKLists(self, lists: List[Optional[ListNode]]) -&gt; Optional[ListNode]:', 'topic': ['Linked Lists', 'Divide and Conquer', 'Sorting'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>['Linked Lists', 'Divide and Conquer', 'Sorting']</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Merge k Sorted Lists</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>You are given an array of k linked-lists lists, each linked-list is sorted in ascending order.
 Merge all the linked-lists into one sorted linked-list and return it.
@@ -1056,7 +1094,7 @@
 The sum of lists[i].length will not exceed 10^4.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>class Solution:
     def mergeKLists(self, lists: List[Optional[ListNode]]) -&gt; Optional[ListNode]:</t>
@@ -1067,27 +1105,30 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'index': 14, 'question name': 'Search in Rotated Sorted Array', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def search(self, nums: List[int], target: int) -&gt; int:', 'topic': ['Array']}</t>
-        </is>
+      <c r="B13" t="n">
+        <v>11</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>{'index': 14, 'question name': 'Search in Rotated Sorted Array', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def search(self, nums: List[int], target: int) -&gt; int:', 'topic': ['Array'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>['Array']</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Search in Rotated Sorted Array</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>There is an integer array nums sorted in ascending order (with distinct values).
 Prior to being passed to your function, nums is possibly rotated at an unknown pivot index k (1 &lt;= k &lt; nums.length) such that the resulting array is [nums[k], nums[k+1], ..., nums[n-1], nums[0], nums[1], ..., nums[k-1]] (0-indexed). For example, [0,1,2,4,5,6,7] might be rotated at pivot index 3 and become [4,5,6,7,0,1,2].
@@ -1110,7 +1151,7 @@
 -10^4 &lt;= target &lt;= 10^4</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>class Solution:
     def search(self, nums: List[int], target: int) -&gt; int:</t>
@@ -1121,27 +1162,30 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'index': 15, 'question name': 'Kth Largest Element in an Array', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def findKthLargest(self, nums: list[int], k: int) -&gt; int:', 'topic': ['Array', 'Divide and Conquer', 'Sorting']}</t>
-        </is>
+      <c r="B14" t="n">
+        <v>12</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>{'index': 15, 'question name': 'Kth Largest Element in an Array', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def findKthLargest(self, nums: list[int], k: int) -&gt; int:', 'topic': ['Array', 'Divide and Conquer', 'Sorting'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>['Array', 'Divide and Conquer', 'Sorting']</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Kth Largest Element in an Array</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Given an integer array nums and an integer k, return the kth largest element in the array.
 Note that it is the kth largest element in the sorted order, not the kth distinct element.
@@ -1157,7 +1201,7 @@
 -10^4 &lt;= nums[i] &lt;= 10^4</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>class Solution:
     def findKthLargest(self, nums: list[int], k: int) -&gt; int:</t>
@@ -1168,27 +1212,30 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'index': 16, 'question name': 'Median of Two Sorted Arrays', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def findMedianSortedArrays(self, nums1: List[int], nums2: List[int]) -&gt; float:', 'topic': ['Array', 'Divide and Conquer']}</t>
-        </is>
+      <c r="B15" t="n">
+        <v>13</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>{'index': 16, 'question name': 'Median of Two Sorted Arrays', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def findMedianSortedArrays(self, nums1: List[int], nums2: List[int]) -&gt; float:', 'topic': ['Array', 'Divide and Conquer'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>['Array', 'Divide and Conquer']</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Median of Two Sorted Arrays</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Given two sorted arrays nums1 and nums2 of size m and n respectively, return the median of the two sorted arrays.
 The overall run time complexity should be O(log (m+n)).
@@ -1209,7 +1256,7 @@
 -10^6 &lt;= nums1[i], nums2[i] &lt;= 10^6</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>class Solution:
     def findMedianSortedArrays(self, nums1: List[int], nums2: List[int]) -&gt; float:</t>
@@ -1220,27 +1267,30 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'index': 17, 'question name': 'Number of Islands', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def numIslands(self, grid: List[List[str]]) -&gt; int:', 'topic': ['Array', 'DFS', 'BFS']}</t>
-        </is>
+      <c r="B16" t="n">
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>{'index': 17, 'question name': 'Number of Islands', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def numIslands(self, grid: List[List[str]]) -&gt; int:', 'topic': ['Array', 'DFS', 'BFS'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>['Array', 'DFS', 'BFS']</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Number of Islands</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Given an m x n 2D binary grid grid which represents a map of '1's (land) and '0's (water), return the number of islands.
 An island is surrounded by water and is formed by connecting adjacent lands horizontally or vertically. You may assume all four edges of the grid are all surrounded by water.
@@ -1267,7 +1317,7 @@
 grid[i][j] is '0' or '1'.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>class Solution:
     def numIslands(self, grid: List[List[str]]) -&gt; int:</t>
@@ -1278,27 +1328,30 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'index': 18, 'question name': 'Clone Graph', 'difficulty': 'Medium', 'entry point': "class Solution:\n    def cloneGraph(self, node: Optional['Node']) -&gt; Optional['Node']:", 'topic': ['DFS', 'BFS', 'Graph']}</t>
-        </is>
+      <c r="B17" t="n">
+        <v>15</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>{'index': 18, 'question name': 'Clone Graph', 'difficulty': 'Medium', 'entry point': "class Solution:\n    def cloneGraph(self, node: Optional['Node']) -&gt; Optional['Node']:", 'topic': ['DFS', 'BFS', 'Graph'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>['DFS', 'BFS', 'Graph']</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Clone Graph</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Given a reference of a node in a connected undirected graph.
 Return a deep copy (clone) of the graph.
@@ -1335,7 +1388,7 @@
 The Graph is connected and all nodes can be visited starting from the given node.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>class Solution:
     def cloneGraph(self, node: Optional['Node']) -&gt; Optional['Node']:</t>
@@ -1346,27 +1399,30 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'index': 19, 'question name': 'Longest Increasing Path in a Matrix', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def longestIncreasingPath(self, matrix: List[List[int]]) -&gt; int:', 'topic': ['Array', 'Dynamic Programming', 'DFS', 'BFS', 'Graph']}</t>
-        </is>
+      <c r="B18" t="n">
+        <v>16</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>{'index': 19, 'question name': 'Longest Increasing Path in a Matrix', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def longestIncreasingPath(self, matrix: List[List[int]]) -&gt; int:', 'topic': ['Array', 'Dynamic Programming', 'DFS', 'BFS', 'Graph'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>['Array', 'Dynamic Programming', 'DFS', 'BFS', 'Graph']</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Longest Increasing Path in a Matrix</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Given an m x n integers matrix, return the length of the longest increasing path in matrix.
 From each cell, you can either move in four directions: left, right, up, or down. You may not move diagonally or move outside the boundary (i.e., wrap-around is not allowed).
@@ -1388,7 +1444,7 @@
 0 &lt;= matrix[i][j] &lt;= 2^31 - 1</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>class Solution:
     def longestIncreasingPath(self, matrix: List[List[int]]) -&gt; int:</t>
@@ -1399,27 +1455,30 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'index': 21, 'question name': 'Binary Tree Right Side View', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def rightSideView(self, root: Optional[TreeNode]) -&gt; List[int]:', 'topic': ['DFS', 'BFS', 'Binary Trees']}</t>
-        </is>
+      <c r="B19" t="n">
+        <v>17</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>{'index': 21, 'question name': 'Binary Tree Right Side View', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def rightSideView(self, root: Optional[TreeNode]) -&gt; List[int]:', 'topic': ['DFS', 'BFS', 'Binary Trees'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>['DFS', 'BFS', 'Binary Trees']</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Binary Tree Right Side View</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Given the root of a binary tree, imagine yourself standing on the right side of it, return the values of the nodes you can see ordered from top to bottom.
 Example 1:
@@ -1441,7 +1500,7 @@
 -100 &lt;= Node.val &lt;= 100</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>class Solution:
     def rightSideView(self, root: Optional[TreeNode]) -&gt; List[int]:</t>
@@ -1450,29 +1509,32 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
         <v>0</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'index': 22, 'question name': 'Course Schedule', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def canFinish(self, numCourses: int, prerequisites: List[List[int]]) -&gt; bool:', 'topic': ['DFS', 'BFS', 'Graph']}</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>{'index': 22, 'question name': 'Course Schedule', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def canFinish(self, numCourses: int, prerequisites: List[List[int]]) -&gt; bool:', 'topic': ['DFS', 'BFS', 'Graph'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>['DFS', 'BFS', 'Graph']</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Course Schedule</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>There are a total of numCourses courses you have to take, labeled from 0 to numCourses - 1. You are given an array prerequisites where prerequisites[i] = [ai, bi] indicates that you must take course bi first if you want to take course ai.
 For example, the pair [0, 1], indicates that to take course 0 you have to first take course 1.
@@ -1495,7 +1557,7 @@
 All the pairs prerequisites[i] are unique.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>class Solution:
     def canFinish(self, numCourses: int, prerequisites: List[List[int]]) -&gt; bool:</t>
@@ -1504,29 +1566,32 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
         <v>1</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'index': 23, 'question name': 'Snakes and Ladders', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def snakesAndLadders(self, board: List[List[int]]) -&gt; int:', 'topic': ['DFS', 'BFS', 'Graph']}</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>{'index': 23, 'question name': 'Snakes and Ladders', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def snakesAndLadders(self, board: List[List[int]]) -&gt; int:', 'topic': ['DFS', 'BFS', 'Graph'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>['DFS', 'BFS', 'Graph']</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Snakes and Ladders</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>You are given an n x n integer matrix board where the cells are labeled from 1 to n2 in a Boustrophedon style starting from the bottom left of the board (i.e. board[n - 1][0]) and alternating direction each row.
 You start on square 1 of the board. In each move, starting from square curr, do the following:
@@ -1558,7 +1623,7 @@
 The squares labeled 1 and n^2 are not the starting points of any snake or ladder.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>class Solution:
     def snakesAndLadders(self, board: List[List[int]]) -&gt; int:</t>
@@ -1567,29 +1632,32 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
         <v>2</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'index': 24, 'question name': 'Word Ladder', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def ladderLength(self, beginWord: str, endWord: str, wordList: list[str]) -&gt; int:', 'topic': ['Array', 'BFS', 'Matrix']}</t>
-        </is>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>{'index': 24, 'question name': 'Word Ladder', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def ladderLength(self, beginWord: str, endWord: str, wordList: list[str]) -&gt; int:', 'topic': ['Array', 'BFS', 'Matrix'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>['Array', 'BFS', 'Matrix']</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Word Ladder</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>A transformation sequence from word beginWord to word endWord using a dictionary wordList is a sequence of words beginWord -&gt; s1 -&gt; s2 -&gt; ... -&gt; sk such that:
 Every adjacent pair of words differs by a single letter.
@@ -1614,7 +1682,7 @@
 All the words in wordList are unique.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>class Solution:
     def ladderLength(self, beginWord: str, endWord: str, wordList: list[str]) -&gt; int:</t>
@@ -1623,29 +1691,32 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
         <v>3</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'index': 25, 'question name': 'Find Minimum in Rotated Sorted Array', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def findMin(self, nums: List[int]) -&gt; int:', 'topic': ['BFS']}</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>{'index': 25, 'question name': 'Find Minimum in Rotated Sorted Array', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def findMin(self, nums: List[int]) -&gt; int:', 'topic': ['BFS'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>['BFS']</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Find Minimum in Rotated Sorted Array</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Suppose an array of length n sorted in ascending order is rotated between 1 and n times. For example, the array nums = [0,1,2,4,5,6,7] might become:
 [4,5,6,7,0,1,2] if it was rotated 4 times.
@@ -1673,7 +1744,7 @@
 nums is sorted and rotated between 1 and n times.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>class Solution:
     def findMin(self, nums: List[int]) -&gt; int:</t>
@@ -1682,29 +1753,32 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
         <v>4</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'index': 26, 'question name': 'Search a 2D Matrix', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def searchMatrix(self, matrix: List[List[int]], target: int) -&gt; bool:', 'topic': ['Array', 'Binary Search']}</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>{'index': 26, 'question name': 'Search a 2D Matrix', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def searchMatrix(self, matrix: List[List[int]], target: int) -&gt; bool:', 'topic': ['Array', 'Binary Search'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>['Array', 'Binary Search']</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Search a 2D Matrix</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>You are given an m x n integer matrix matrix with the following two properties:
 Each row is sorted in non-decreasing order.
@@ -1724,7 +1798,7 @@
 -104 &lt;= matrix[i][j], target &lt;= 10^4</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>class Solution:
     def searchMatrix(self, matrix: List[List[int]], target: int) -&gt; bool:</t>
@@ -1733,29 +1807,32 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
         <v>5</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'index': 27, 'question name': 'Median of Two Sorted Arrays', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def findMedianSortedArrays(self, nums1: List[int], nums2: List[int]) -&gt; float:', 'topic': ['Array', 'Binary Search', 'Matrix']}</t>
-        </is>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>{'index': 27, 'question name': 'Median of Two Sorted Arrays', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def findMedianSortedArrays(self, nums1: List[int], nums2: List[int]) -&gt; float:', 'topic': ['Array', 'Binary Search', 'Matrix'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>['Array', 'Binary Search', 'Matrix']</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Median of Two Sorted Arrays</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Given two sorted arrays nums1 and nums2 of size m and n respectively, return the median of the two sorted arrays.
 The overall run time complexity should be O(log (m+n)).
@@ -1776,7 +1853,7 @@
 -10^6 &lt;= nums1[i], nums2[i] &lt;= 10^6</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>class Solution:
     def findMedianSortedArrays(self, nums1: List[int], nums2: List[int]) -&gt; float:</t>
@@ -1785,29 +1862,32 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
         <v>6</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'index': 28, 'question name': 'Find Peak Element', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def findPeakElement(self, nums: List[int]) -&gt; int:', 'topic': ['Array', 'Binary Search']}</t>
-        </is>
-      </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>{'index': 28, 'question name': 'Find Peak Element', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def findPeakElement(self, nums: List[int]) -&gt; int:', 'topic': ['Array', 'Binary Search'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>['Array', 'Binary Search']</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Find Peak Element</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>A peak element is an element that is strictly greater than its neighbors.
 Given a 0-indexed integer array nums, find a peak element, and return its index. If the array contains multiple peaks, return the index to any of the peaks.
@@ -1827,7 +1907,7 @@
 nums[i] != nums[i + 1] for all valid i.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>class Solution:
     def findPeakElement(self, nums: List[int]) -&gt; int:</t>
@@ -1836,29 +1916,32 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
         <v>7</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'index': 29, 'question name': 'Container With Most Water', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def maxArea(self, height: List[int]) -&gt; int:', 'topic': ['Array', 'Two Pointers', 'Greedy']}</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>{'index': 29, 'question name': 'Container With Most Water', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def maxArea(self, height: List[int]) -&gt; int:', 'topic': ['Array', 'Two Pointers', 'Greedy'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>['Array', 'Two Pointers', 'Greedy']</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>You are given an integer array height of length n. There are n vertical lines drawn such that the two endpoints of the ith line are (i, 0) and (i, height[i]).
 Find two lines that together with the x-axis form a container, such that the container contains the most water.
@@ -1877,7 +1960,7 @@
 0 &lt;= height[i] &lt;= 10^4</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>class Solution:
     def maxArea(self, height: List[int]) -&gt; int:</t>
@@ -1886,29 +1969,32 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
         <v>8</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'index': 30, 'question name': 'Three Sum', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def threeSum(self, nums: List[int]) -&gt; List[List[int]]:        ', 'topic': ['Array', 'Two Pointers', 'Sorting']}</t>
-        </is>
-      </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>{'index': 30, 'question name': 'Three Sum', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def threeSum(self, nums: List[int]) -&gt; List[List[int]]:        ', 'topic': ['Array', 'Two Pointers', 'Sorting'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>['Array', 'Two Pointers', 'Sorting']</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Three Sum</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Given an integer array nums, return all the triplets [nums[i], nums[j], nums[k]] such that i != j, i != k, and j != k, and nums[i] + nums[j] + nums[k] == 0.
 Notice that the solution set must not contain duplicate triplets.
@@ -1934,7 +2020,7 @@
 -10^5 &lt;= nums[i] &lt;= 10^5</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution:
     def threeSum(self, nums: List[int]) -&gt; List[List[int]]:        </t>
@@ -1943,29 +2029,32 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
         <v>9</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'index': 31, 'question name': 'Remove Duplicates from Sorted Array II', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def removeDuplicates(self, nums: List[int]) -&gt; int:', 'topic': ['Array', 'Two Pointers']}</t>
-        </is>
-      </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>{'index': 31, 'question name': 'Remove Duplicates from Sorted Array II', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def removeDuplicates(self, nums: List[int]) -&gt; int:', 'topic': ['Array', 'Two Pointers'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>['Array', 'Two Pointers']</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Remove Duplicates from Sorted Array II</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Given an integer array nums sorted in non-decreasing order, remove some duplicates in-place such that each unique element appears at most twice. The relative order of the elements should be kept the same.
 Since it is impossible to change the length of the array in some languages, you must instead have the result be placed in the first part of the array nums. More formally, if there are k elements after removing the duplicates, then the first k elements of nums should hold the final result. It does not matter what you leave beyond the first k elements.
@@ -1997,7 +2086,7 @@
 nums is sorted in non-decreasing order.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>class Solution:
     def removeDuplicates(self, nums: List[int]) -&gt; int:</t>
@@ -2006,29 +2095,32 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
         <v>10</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'index': 32, 'question name': 'Trapping Rain Water', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def trap(self, height: List[int]) -&gt; int:', 'topic': ['Array', 'Two Pointers', 'Dynamic Programming']}</t>
-        </is>
-      </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>{'index': 32, 'question name': 'Trapping Rain Water', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def trap(self, height: List[int]) -&gt; int:', 'topic': ['Array', 'Two Pointers', 'Dynamic Programming'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>['Array', 'Two Pointers', 'Dynamic Programming']</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Trapping Rain Water</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Given n non-negative integers representing an elevation map where the width of each bar is 1, compute how much water it can trap after raining.
 Example 1:
@@ -2044,7 +2136,7 @@
 0 &lt;= height[i] &lt;= 10^5</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>class Solution:
     def trap(self, height: List[int]) -&gt; int:</t>
@@ -2053,29 +2145,32 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
         <v>11</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'index': 33, 'question name': 'Longest Substring Without Repeating Characters', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def lengthOfLongestSubstring(self, s: str) -&gt; int:', 'topic': ['Sliding Window']}</t>
-        </is>
-      </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>{'index': 33, 'question name': 'Longest Substring Without Repeating Characters', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def lengthOfLongestSubstring(self, s: str) -&gt; int:', 'topic': ['Sliding Window'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>['Sliding Window']</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Given a string s, find the length of the longest substring without duplicate characters.
 Example 1:
@@ -2096,7 +2191,7 @@
 s consists of English letters, digits, symbols and spaces.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>class Solution:
     def lengthOfLongestSubstring(self, s: str) -&gt; int:</t>
@@ -2105,29 +2200,32 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
         <v>12</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'index': 34, 'question name': 'Minimum Window Substring', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def minWindow(self, s: str, t: str) -&gt; str:', 'topic': ['Sliding Window']}</t>
-        </is>
-      </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>{'index': 34, 'question name': 'Minimum Window Substring', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def minWindow(self, s: str, t: str) -&gt; str:', 'topic': ['Sliding Window'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>['Sliding Window']</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Minimum Window Substring</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Given two strings s and t of lengths m and n respectively, return the minimum window substring of s such that every character in t (including duplicates) is included in the window. If there is no such substring, return the empty string "".
 The testcases will be generated such that the answer is unique.
@@ -2151,7 +2249,7 @@
 s and t consist of uppercase and lowercase English letters.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>class Solution:
     def minWindow(self, s: str, t: str) -&gt; str:</t>
@@ -2160,29 +2258,32 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
         <v>13</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'index': 35, 'question name': 'Sliding Window Maximum', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def maxSlidingWindow(self, nums: List[int], k: int) -&gt; List[int]:', 'topic': ['Array', 'Sliding Window']}</t>
-        </is>
-      </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>{'index': 35, 'question name': 'Sliding Window Maximum', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def maxSlidingWindow(self, nums: List[int], k: int) -&gt; List[int]:', 'topic': ['Array', 'Sliding Window'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>['Array', 'Sliding Window']</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Sliding Window Maximum</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>You are given an array of integers nums, there is a sliding window of size k which is moving from the very left of the array to the very right. You can only see the k numbers in the window. Each time the sliding window moves right by one position.
 Return the max sliding window.
@@ -2207,7 +2308,7 @@
 1 &lt;= k &lt;= nums.length</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>class Solution:
     def maxSlidingWindow(self, nums: List[int], k: int) -&gt; List[int]:</t>
@@ -2216,29 +2317,32 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
         <v>14</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'index': 36, 'question name': 'Permutation in String', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def checkInclusion(self, s1: str, s2: str) -&gt; bool:', 'topic': ['Two Pointers', 'Sliding Window']}</t>
-        </is>
-      </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>{'index': 36, 'question name': 'Permutation in String', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def checkInclusion(self, s1: str, s2: str) -&gt; bool:', 'topic': ['Two Pointers', 'Sliding Window'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>['Two Pointers', 'Sliding Window']</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Permutation in String</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Given two strings s1 and s2, return true if s2 contains a permutation of s1, or false otherwise.
 In other words, return true if one of s1's permutations is the substring of s2.
@@ -2254,7 +2358,7 @@
 s1 and s2 consist of lowercase English letters.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>class Solution:
     def checkInclusion(self, s1: str, s2: str) -&gt; bool:</t>
@@ -2263,29 +2367,32 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
         <v>15</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'index': 37, 'question name': 'Reverse Bits', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def reverseBits(self, n: int) -&gt; int:', 'topic': ['Divide and Conquer', 'Bit manipulation']}</t>
-        </is>
-      </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>{'index': 37, 'question name': 'Reverse Bits', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def reverseBits(self, n: int) -&gt; int:', 'topic': ['Divide and Conquer', 'Bit manipulation'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>['Divide and Conquer', 'Bit manipulation']</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Reverse Bits</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Reverse bits of a given 32 bits unsigned integer.
 Example 1:
@@ -2300,7 +2407,7 @@
 The input must be a binary string of length 32</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>class Solution:
     def reverseBits(self, n: int) -&gt; int:</t>
@@ -2309,29 +2416,32 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
         <v>16</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'index': 38, 'question name': 'Maximum XOR of Two Numbers in an Array', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def findMaximumXOR(self, nums: List[int]) -&gt; int:', 'topic': ['Array', 'Bit manipulation']}</t>
-        </is>
-      </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>{'index': 38, 'question name': 'Maximum XOR of Two Numbers in an Array', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def findMaximumXOR(self, nums: List[int]) -&gt; int:', 'topic': ['Array', 'Bit manipulation'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>['Array', 'Bit manipulation']</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Maximum XOR of Two Numbers in an Array</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Given an integer array nums, return the maximum result of nums[i] XOR nums[j], where 0 &lt;= i &lt;= j &lt; n.
 Example 1:
@@ -2346,7 +2456,7 @@
 0 &lt;= nums[i] &lt;= 2^31 - 1</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>class Solution:
     def findMaximumXOR(self, nums: List[int]) -&gt; int:</t>
@@ -2355,29 +2465,32 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
         <v>17</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'index': 39, 'question name': 'Merge K Sorted Lists', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def mergeKLists(self, lists: List[Optional[ListNode]]) -&gt; Optional[ListNode]:', 'topic': ['Linked Lists', 'Divide and Conquer']}</t>
-        </is>
-      </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>{'index': 39, 'question name': 'Merge K Sorted Lists', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def mergeKLists(self, lists: List[Optional[ListNode]]) -&gt; Optional[ListNode]:', 'topic': ['Linked Lists', 'Divide and Conquer'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>['Linked Lists', 'Divide and Conquer']</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Merge K Sorted Lists</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>You are given an array of k linked-lists lists, each linked-list is sorted in ascending order.
 Merge all the linked-lists into one sorted linked-list and return it.
@@ -2407,7 +2520,7 @@
 The sum of lists[i].length will not exceed 10^4.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>class Solution:
     def mergeKLists(self, lists: List[Optional[ListNode]]) -&gt; Optional[ListNode]:</t>
@@ -2416,29 +2529,32 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
         <v>18</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'index': 40, 'question name': 'Reverse Nodes in k-Group', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def reverseKGroup(self, head: Optional[ListNode], k: int) -&gt; Optional[ListNode]:', 'topic': ['Linked Lists']}</t>
-        </is>
-      </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>{'index': 40, 'question name': 'Reverse Nodes in k-Group', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def reverseKGroup(self, head: Optional[ListNode], k: int) -&gt; Optional[ListNode]:', 'topic': ['Linked Lists'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>['Linked Lists']</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Reverse Nodes in k-Group</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Given the head of a linked list, reverse the nodes of the list k at a time, and return the modified list.
 k is a positive integer and is less than or equal to the length of the linked list. If the number of nodes is not a multiple of k then left-out nodes, in the end, should remain as it is.
@@ -2455,7 +2571,7 @@
 0 &lt;= Node.val &lt;= 1000</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>class Solution:
     def reverseKGroup(self, head: Optional[ListNode], k: int) -&gt; Optional[ListNode]:</t>
@@ -2464,29 +2580,32 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
         <v>19</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'index': 41, 'question name': 'Flatten Binary Tree to Linked List', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def flatten(self, root: Optional[TreeNode]) -&gt; None:\n        """\n        Do not return anything, modify root in-place instead.\n        """', 'topic': ['Linked Lists', 'Binary Search']}</t>
-        </is>
-      </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>{'index': 41, 'question name': 'Flatten Binary Tree to Linked List', 'difficulty': 'Medium', 'entry point': 'class Solution:\n    def flatten(self, root: Optional[TreeNode]) -&gt; None:\n        """\n        Do not return anything, modify root in-place instead.\n        """', 'topic': ['Linked Lists', 'Binary Search'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>['Linked Lists', 'Binary Search']</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Flatten Binary Tree to Linked List</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Given the root of a binary tree, flatten the tree into a "linked list":
 The "linked list" should use the same TreeNode class where the right child pointer points to the next node in the list and the left child pointer is always null.
@@ -2505,7 +2624,7 @@
 -100 &lt;= Node.val &lt;= 100</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>class Solution:
     def flatten(self, root: Optional[TreeNode]) -&gt; None:
@@ -2517,29 +2636,32 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
         <v>20</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'index': 42, 'question name': 'Binary Tree Maximum Path Sum', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def maxPathSum(self, root: Optional[TreeNode]) -&gt; int:', 'topic': ['Binary Trees', 'Dynamic Programming', 'DFS']}</t>
-        </is>
-      </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>{'index': 42, 'question name': 'Binary Tree Maximum Path Sum', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def maxPathSum(self, root: Optional[TreeNode]) -&gt; int:', 'topic': ['Binary Trees', 'Dynamic Programming', 'DFS'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>['Binary Trees', 'Dynamic Programming', 'DFS']</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Binary Tree Maximum Path Sum</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>A path in a binary tree is a sequence of nodes where each pair of adjacent nodes in the sequence has an edge connecting them. A node can only appear in the sequence at most once. Note that the path does not need to pass through the root.
 The path sum of a path is the sum of the node's values in the path.
@@ -2557,7 +2679,7 @@
 -1000 &lt;= Node.val &lt;= 1000</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>class Solution:
     def maxPathSum(self, root: Optional[TreeNode]) -&gt; int:</t>
@@ -2566,29 +2688,32 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
         <v>21</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'index': 43, 'question name': 'Binary Tree Cameras', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def minCameraCover(self, root: Optional[TreeNode]) -&gt; int:', 'topic': ['Dynamic Programming', 'Binary Trees', 'DFS']}</t>
-        </is>
-      </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>{'index': 43, 'question name': 'Binary Tree Cameras', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def minCameraCover(self, root: Optional[TreeNode]) -&gt; int:', 'topic': ['Dynamic Programming', 'Binary Trees', 'DFS'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>['Dynamic Programming', 'Binary Trees', 'DFS']</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Binary Tree Cameras</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>You are given the root of a binary tree. We install cameras on the tree nodes where each camera at a node can monitor its parent, itself, and its immediate children.
 Return the minimum number of cameras needed to monitor all nodes of the tree.
@@ -2603,7 +2728,7 @@
 Node.val == 0</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>class Solution:
     def minCameraCover(self, root: Optional[TreeNode]) -&gt; int:</t>
@@ -2612,29 +2737,32 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
         <v>22</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'index': 44, 'question name': 'Vertical Order Traversal of a Binary Tree', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def verticalTraversal(self, root: Optional[TreeNode]) -&gt; List[List[int]]:', 'topic': ['DFS', 'BFS', 'Sorting', 'Binary Trees']}</t>
-        </is>
-      </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>{'index': 44, 'question name': 'Vertical Order Traversal of a Binary Tree', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def verticalTraversal(self, root: Optional[TreeNode]) -&gt; List[List[int]]:', 'topic': ['DFS', 'BFS', 'Sorting', 'Binary Trees'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>['DFS', 'BFS', 'Sorting', 'Binary Trees']</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Vertical Order Traversal of a Binary Tree</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Given the root of a binary tree, calculate the vertical order traversal of the binary tree.
 For each node at position (row, col), its left and right children will be at positions (row + 1, col - 1) and (row + 1, col + 1) respectively. The root of the tree is at (0, 0).
@@ -2670,7 +2798,7 @@
 0 &lt;= Node.val &lt;= 1000</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>class Solution:
     def verticalTraversal(self, root: Optional[TreeNode]) -&gt; List[List[int]]:</t>
@@ -2679,29 +2807,32 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
         <v>23</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'index': 45, 'question name': 'Recover a Tree from PreOrder Traversal', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def recoverFromPreorder(self, traversal: str) -&gt; Optional[TreeNode]:', 'topic': ['Binary Trees', 'DFS']}</t>
-        </is>
-      </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>{'index': 45, 'question name': 'Recover a Tree from PreOrder Traversal', 'difficulty': 'Hard', 'entry point': 'class Solution:\n    def recoverFromPreorder(self, traversal: str) -&gt; Optional[TreeNode]:', 'topic': ['Binary Trees', 'DFS'], 'source': 'leetcode'}</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>['Binary Trees', 'DFS']</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Recover a Tree from PreOrder Traversal</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>We run a preorder depth-first search (DFS) on the root of a binary tree.
 At each node in this traversal, we output D dashes (where D is the depth of this node), then we output the value of this node.  If the depth of a node is D, the depth of its immediate child is D + 1.  The depth of the root node is 0.
@@ -2721,7 +2852,7 @@
 1 &lt;= Node.val &lt;= 109</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>class Solution:
     def recoverFromPreorder(self, traversal: str) -&gt; Optional[TreeNode]:</t>
